--- a/personal_forms/009_household_information_form--personal_forms.xlsx
+++ b/personal_forms/009_household_information_form--personal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'married',_'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'married', 'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'small', 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'large', 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'work',_'label':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'work', 'label': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'investment',_'label':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'investment', 'label': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'government',_'label':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'government', 'label': 'Government'}</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'student',_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'student', 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'employee',_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'employee', 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'retired',_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'retired', 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'engineer',_'label':_'engineer'}</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'engineer', 'label': 'Engineer'}</t>
+          <t>Engineer</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'doctor',_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'doctor', 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'artist',_'label':_'artist'}</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'artist', 'label': 'Artist'}</t>
+          <t>Artist</t>
         </is>
       </c>
     </row>
